--- a/content/members.xlsx
+++ b/content/members.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>type</t>
   </si>
@@ -25,6 +25,9 @@
     <t>林小满</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>周予</t>
   </si>
   <si>
@@ -64,16 +67,31 @@
     <t>vocal</t>
   </si>
   <si>
+    <t>唱功型</t>
+  </si>
+  <si>
     <t>dance</t>
   </si>
   <si>
+    <t>舞蹈型</t>
+  </si>
+  <si>
     <t>acting</t>
   </si>
   <si>
+    <t>演技型</t>
+  </si>
+  <si>
     <t>talk</t>
   </si>
   <si>
+    <t>口才型</t>
+  </si>
+  <si>
     <t>balanced</t>
+  </si>
+  <si>
+    <t>均衡型</t>
   </si>
 </sst>
 </file>
@@ -459,155 +477,210 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
       <c r="B15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/content/members.xlsx
+++ b/content/members.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
   <si>
     <t>type</t>
   </si>
@@ -59,6 +59,66 @@
   </si>
   <si>
     <t>叶绫</t>
+  </si>
+  <si>
+    <t>温言</t>
+  </si>
+  <si>
+    <t>宋迟</t>
+  </si>
+  <si>
+    <t>吴念</t>
+  </si>
+  <si>
+    <t>钱多多</t>
+  </si>
+  <si>
+    <t>冯岚</t>
+  </si>
+  <si>
+    <t>蒋野</t>
+  </si>
+  <si>
+    <t>韩星</t>
+  </si>
+  <si>
+    <t>曹云</t>
+  </si>
+  <si>
+    <t>邓柯</t>
+  </si>
+  <si>
+    <t>钟离</t>
+  </si>
+  <si>
+    <t>方糖</t>
+  </si>
+  <si>
+    <t>阮青禾</t>
+  </si>
+  <si>
+    <t>谢遥</t>
+  </si>
+  <si>
+    <t>施然</t>
+  </si>
+  <si>
+    <t>崔羽</t>
+  </si>
+  <si>
+    <t>范屿</t>
+  </si>
+  <si>
+    <t>彭野</t>
+  </si>
+  <si>
+    <t>董夏</t>
+  </si>
+  <si>
+    <t>袁清</t>
+  </si>
+  <si>
+    <t>陆听</t>
   </si>
   <si>
     <t>bias</t>
@@ -477,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -630,57 +690,277 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
         <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
